--- a/artfynd/A 37422-2024 artfynd.xlsx
+++ b/artfynd/A 37422-2024 artfynd.xlsx
@@ -1867,10 +1867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119930953</v>
+        <v>119930894</v>
       </c>
       <c r="B12" t="n">
-        <v>91840</v>
+        <v>4772</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1883,28 +1883,33 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>102306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rökenskärr, Srm</t>
@@ -1946,7 +1951,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1956,7 +1961,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1983,10 +1988,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119930894</v>
+        <v>119930953</v>
       </c>
       <c r="B13" t="n">
-        <v>4772</v>
+        <v>91840</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1999,33 +2004,28 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102306</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>51</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rökenskärr, Srm</t>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2104,10 +2104,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119930933</v>
+        <v>119930913</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
+        <v>90966</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2120,25 +2120,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2147,10 +2151,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581271</v>
+        <v>581228</v>
       </c>
       <c r="R14" t="n">
-        <v>6509584</v>
+        <v>6509602</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2182,7 +2186,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2192,7 +2196,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2219,10 +2223,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119930913</v>
+        <v>119930933</v>
       </c>
       <c r="B15" t="n">
-        <v>90966</v>
+        <v>91840</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2235,29 +2239,25 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581228</v>
+        <v>581271</v>
       </c>
       <c r="R15" t="n">
-        <v>6509602</v>
+        <v>6509584</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2338,10 +2338,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119930905</v>
+        <v>119930939</v>
       </c>
       <c r="B16" t="n">
-        <v>57463</v>
+        <v>91884</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2354,21 +2354,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>5449</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2376,24 +2376,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581280</v>
+        <v>581163</v>
       </c>
       <c r="R16" t="n">
-        <v>6509285</v>
+        <v>6509559</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2425,7 +2420,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2435,7 +2430,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2462,10 +2457,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119930939</v>
+        <v>119930905</v>
       </c>
       <c r="B17" t="n">
-        <v>91884</v>
+        <v>57463</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2478,21 +2473,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2500,19 +2495,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581163</v>
+        <v>581280</v>
       </c>
       <c r="R17" t="n">
-        <v>6509559</v>
+        <v>6509285</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 37422-2024 artfynd.xlsx
+++ b/artfynd/A 37422-2024 artfynd.xlsx
@@ -1867,10 +1867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119930894</v>
+        <v>119930953</v>
       </c>
       <c r="B12" t="n">
-        <v>4772</v>
+        <v>91840</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1883,33 +1883,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102306</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>51</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rökenskärr, Srm</t>
@@ -1951,7 +1946,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1961,7 +1956,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1988,10 +1983,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119930953</v>
+        <v>119930894</v>
       </c>
       <c r="B13" t="n">
-        <v>91840</v>
+        <v>4772</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2004,28 +1999,33 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>102306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rökenskärr, Srm</t>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2338,10 +2338,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119930939</v>
+        <v>119930905</v>
       </c>
       <c r="B16" t="n">
-        <v>91884</v>
+        <v>57463</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2354,21 +2354,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2376,19 +2376,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581163</v>
+        <v>581280</v>
       </c>
       <c r="R16" t="n">
-        <v>6509559</v>
+        <v>6509285</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2420,7 +2425,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2430,7 +2435,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2457,10 +2462,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119930905</v>
+        <v>119930939</v>
       </c>
       <c r="B17" t="n">
-        <v>57463</v>
+        <v>91884</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2473,21 +2478,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>5449</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2495,24 +2500,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581280</v>
+        <v>581163</v>
       </c>
       <c r="R17" t="n">
-        <v>6509285</v>
+        <v>6509559</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 37422-2024 artfynd.xlsx
+++ b/artfynd/A 37422-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119930945</v>
+        <v>119930955</v>
       </c>
       <c r="B2" t="n">
         <v>94681</v>
@@ -710,26 +710,22 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581292</v>
+        <v>581280</v>
       </c>
       <c r="R2" t="n">
-        <v>6509594</v>
+        <v>6509285</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119930949</v>
+        <v>119930945</v>
       </c>
       <c r="B3" t="n">
         <v>94681</v>
@@ -828,7 +824,11 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -839,13 +839,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581228</v>
+        <v>581292</v>
       </c>
       <c r="R3" t="n">
-        <v>6509602</v>
+        <v>6509594</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119930921</v>
+        <v>119930948</v>
       </c>
       <c r="B4" t="n">
-        <v>91185</v>
+        <v>94681</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,30 +927,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6031</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -958,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581280</v>
+        <v>581271</v>
       </c>
       <c r="R4" t="n">
-        <v>6509285</v>
+        <v>6509584</v>
       </c>
       <c r="S4" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119930948</v>
+        <v>119930907</v>
       </c>
       <c r="B5" t="n">
-        <v>94681</v>
+        <v>58166</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,27 +1043,32 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>208249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1074,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581271</v>
+        <v>581287</v>
       </c>
       <c r="R5" t="n">
-        <v>6509584</v>
+        <v>6509543</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1109,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119930930</v>
+        <v>119930939</v>
       </c>
       <c r="B6" t="n">
-        <v>91836</v>
+        <v>91884</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,28 +1160,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4363</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1189,10 +1195,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581271</v>
+        <v>581163</v>
       </c>
       <c r="R6" t="n">
-        <v>6509584</v>
+        <v>6509559</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1224,7 +1230,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1240,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,10 +1267,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119930944</v>
+        <v>119930933</v>
       </c>
       <c r="B7" t="n">
-        <v>94681</v>
+        <v>91840</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,31 +1283,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1309,13 +1310,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581299</v>
+        <v>581271</v>
       </c>
       <c r="R7" t="n">
-        <v>6509583</v>
+        <v>6509584</v>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1344,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,12 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2 kuddar</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119930955</v>
+        <v>119930929</v>
       </c>
       <c r="B8" t="n">
-        <v>94681</v>
+        <v>91836</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,38 +1398,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>4363</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581280</v>
+        <v>581271</v>
       </c>
       <c r="R8" t="n">
-        <v>6509285</v>
+        <v>6509584</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1465,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1475,7 +1470,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,10 +1497,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119930907</v>
+        <v>119930950</v>
       </c>
       <c r="B9" t="n">
-        <v>58166</v>
+        <v>91840</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,43 +1513,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208249</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581287</v>
+        <v>581280</v>
       </c>
       <c r="R9" t="n">
-        <v>6509543</v>
+        <v>6509285</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1586,7 +1576,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1596,7 +1586,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1623,10 +1613,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119930923</v>
+        <v>119930952</v>
       </c>
       <c r="B10" t="n">
-        <v>91836</v>
+        <v>96865</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1639,45 +1629,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4363</v>
+        <v>221946</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581280</v>
+        <v>581256</v>
       </c>
       <c r="R10" t="n">
-        <v>6509285</v>
+        <v>6509395</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1709,7 +1696,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1719,7 +1706,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1746,10 +1733,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119930900</v>
+        <v>119930913</v>
       </c>
       <c r="B11" t="n">
-        <v>5189</v>
+        <v>90966</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1762,32 +1749,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>5420</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1830,7 +1815,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1840,7 +1825,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1867,10 +1852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119930953</v>
+        <v>119930936</v>
       </c>
       <c r="B12" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1879,45 +1864,44 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581280</v>
+        <v>581269</v>
       </c>
       <c r="R12" t="n">
-        <v>6509285</v>
+        <v>6509448</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1946,7 +1930,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1956,7 +1940,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1983,10 +1967,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119930894</v>
+        <v>119930944</v>
       </c>
       <c r="B13" t="n">
-        <v>4772</v>
+        <v>94681</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1999,46 +1983,45 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102306</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581280</v>
+        <v>581299</v>
       </c>
       <c r="R13" t="n">
-        <v>6509285</v>
+        <v>6509583</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2067,7 +2050,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2077,7 +2060,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2 kuddar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2104,10 +2092,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119930913</v>
+        <v>119930921</v>
       </c>
       <c r="B14" t="n">
-        <v>90966</v>
+        <v>91185</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2120,29 +2108,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5420</v>
+        <v>6031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2151,13 +2139,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581228</v>
+        <v>581280</v>
       </c>
       <c r="R14" t="n">
-        <v>6509602</v>
+        <v>6509285</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2186,7 +2174,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2196,7 +2184,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2223,10 +2211,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119930933</v>
+        <v>119930938</v>
       </c>
       <c r="B15" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2235,41 +2223,45 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581271</v>
+        <v>581280</v>
       </c>
       <c r="R15" t="n">
-        <v>6509584</v>
+        <v>6509285</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2301,7 +2293,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2311,7 +2303,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2462,10 +2454,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119930939</v>
+        <v>119930949</v>
       </c>
       <c r="B17" t="n">
-        <v>91884</v>
+        <v>94681</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2474,34 +2466,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2509,13 +2498,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581163</v>
+        <v>581228</v>
       </c>
       <c r="R17" t="n">
-        <v>6509559</v>
+        <v>6509602</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2544,7 +2533,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2554,7 +2543,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2581,10 +2570,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119930936</v>
+        <v>119930937</v>
       </c>
       <c r="B18" t="n">
-        <v>91863</v>
+        <v>91884</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2597,24 +2586,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2624,13 +2617,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581269</v>
+        <v>581288</v>
       </c>
       <c r="R18" t="n">
-        <v>6509448</v>
+        <v>6509503</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2659,7 +2652,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2669,7 +2662,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2696,10 +2689,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119930952</v>
+        <v>119930923</v>
       </c>
       <c r="B19" t="n">
-        <v>96865</v>
+        <v>91836</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2712,42 +2705,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221946</v>
+        <v>4363</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581256</v>
+        <v>581280</v>
       </c>
       <c r="R19" t="n">
-        <v>6509395</v>
+        <v>6509285</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2779,7 +2775,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2789,7 +2785,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2816,10 +2812,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119930937</v>
+        <v>119930894</v>
       </c>
       <c r="B20" t="n">
-        <v>91884</v>
+        <v>4772</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2828,25 +2824,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5449</v>
+        <v>102306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2856,17 +2852,19 @@
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581288</v>
+        <v>581280</v>
       </c>
       <c r="R20" t="n">
-        <v>6509503</v>
+        <v>6509285</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2898,7 +2896,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2908,7 +2906,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2935,10 +2933,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119930938</v>
+        <v>119930900</v>
       </c>
       <c r="B21" t="n">
-        <v>91884</v>
+        <v>5189</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2947,45 +2945,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>105930</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581280</v>
+        <v>581228</v>
       </c>
       <c r="R21" t="n">
-        <v>6509285</v>
+        <v>6509602</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 37422-2024 artfynd.xlsx
+++ b/artfynd/A 37422-2024 artfynd.xlsx
@@ -2330,10 +2330,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119930905</v>
+        <v>119930949</v>
       </c>
       <c r="B16" t="n">
-        <v>57463</v>
+        <v>94681</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2342,53 +2342,45 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581280</v>
+        <v>581228</v>
       </c>
       <c r="R16" t="n">
-        <v>6509285</v>
+        <v>6509602</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2417,7 +2409,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2427,7 +2419,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2454,10 +2446,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119930949</v>
+        <v>119930937</v>
       </c>
       <c r="B17" t="n">
-        <v>94681</v>
+        <v>91884</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2466,31 +2458,34 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2498,13 +2493,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581228</v>
+        <v>581288</v>
       </c>
       <c r="R17" t="n">
-        <v>6509602</v>
+        <v>6509503</v>
       </c>
       <c r="S17" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2533,7 +2528,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2543,7 +2538,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2570,10 +2565,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119930937</v>
+        <v>119930905</v>
       </c>
       <c r="B18" t="n">
-        <v>91884</v>
+        <v>57463</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2586,21 +2581,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2608,19 +2603,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581288</v>
+        <v>581280</v>
       </c>
       <c r="R18" t="n">
-        <v>6509503</v>
+        <v>6509285</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2812,10 +2812,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119930894</v>
+        <v>119930900</v>
       </c>
       <c r="B20" t="n">
-        <v>4772</v>
+        <v>5189</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2828,21 +2828,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2857,14 +2857,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581280</v>
+        <v>581228</v>
       </c>
       <c r="R20" t="n">
-        <v>6509285</v>
+        <v>6509602</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2933,10 +2933,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119930900</v>
+        <v>119930894</v>
       </c>
       <c r="B21" t="n">
-        <v>5189</v>
+        <v>4772</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2949,21 +2949,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2978,14 +2978,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581228</v>
+        <v>581280</v>
       </c>
       <c r="R21" t="n">
-        <v>6509602</v>
+        <v>6509285</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 37422-2024 artfynd.xlsx
+++ b/artfynd/A 37422-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119930955</v>
+        <v>119930953</v>
       </c>
       <c r="B2" t="n">
-        <v>94681</v>
+        <v>91840</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>51</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119930945</v>
+        <v>119930929</v>
       </c>
       <c r="B3" t="n">
-        <v>94681</v>
+        <v>91836</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,31 +807,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>4363</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,13 +834,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581292</v>
+        <v>581271</v>
       </c>
       <c r="R3" t="n">
-        <v>6509594</v>
+        <v>6509584</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119930948</v>
+        <v>119930905</v>
       </c>
       <c r="B4" t="n">
-        <v>94681</v>
+        <v>57463</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,42 +918,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581271</v>
+        <v>581280</v>
       </c>
       <c r="R4" t="n">
-        <v>6509584</v>
+        <v>6509285</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -990,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119930907</v>
+        <v>119930936</v>
       </c>
       <c r="B5" t="n">
-        <v>58166</v>
+        <v>91863</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,36 +1042,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208249</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1076,13 +1073,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581287</v>
+        <v>581269</v>
       </c>
       <c r="R5" t="n">
-        <v>6509543</v>
+        <v>6509448</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1111,7 +1108,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1118,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119930939</v>
+        <v>119930955</v>
       </c>
       <c r="B6" t="n">
-        <v>91884</v>
+        <v>94681</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,45 +1157,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581163</v>
+        <v>581280</v>
       </c>
       <c r="R6" t="n">
-        <v>6509559</v>
+        <v>6509285</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1230,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1240,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119930933</v>
+        <v>119930945</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
+        <v>94681</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,26 +1277,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1310,13 +1309,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581271</v>
+        <v>581292</v>
       </c>
       <c r="R7" t="n">
-        <v>6509584</v>
+        <v>6509594</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119930929</v>
+        <v>119930948</v>
       </c>
       <c r="B8" t="n">
-        <v>91836</v>
+        <v>94681</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,26 +1397,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4363</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,10 +1497,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119930950</v>
+        <v>119930938</v>
       </c>
       <c r="B9" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,32 +1509,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rökenskärr, Srm</t>
@@ -1576,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1586,7 +1589,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1733,10 +1736,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119930913</v>
+        <v>119930944</v>
       </c>
       <c r="B11" t="n">
-        <v>90966</v>
+        <v>94681</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1749,30 +1752,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1780,13 +1784,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581228</v>
+        <v>581299</v>
       </c>
       <c r="R11" t="n">
-        <v>6509602</v>
+        <v>6509583</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1815,7 +1819,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1825,7 +1829,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2 kuddar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,10 +1861,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119930936</v>
+        <v>119930921</v>
       </c>
       <c r="B12" t="n">
-        <v>91863</v>
+        <v>91185</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1864,28 +1873,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1895,13 +1908,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581269</v>
+        <v>581280</v>
       </c>
       <c r="R12" t="n">
-        <v>6509448</v>
+        <v>6509285</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1930,7 +1943,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1940,7 +1953,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1967,10 +1980,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119930944</v>
+        <v>119930939</v>
       </c>
       <c r="B13" t="n">
-        <v>94681</v>
+        <v>91884</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1979,35 +1992,34 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2015,13 +2027,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581299</v>
+        <v>581163</v>
       </c>
       <c r="R13" t="n">
-        <v>6509583</v>
+        <v>6509559</v>
       </c>
       <c r="S13" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2050,7 +2062,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2060,12 +2072,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2 kuddar</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2092,10 +2099,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119930921</v>
+        <v>119930900</v>
       </c>
       <c r="B14" t="n">
-        <v>91185</v>
+        <v>5189</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2108,21 +2115,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6031</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2132,6 +2139,8 @@
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2139,13 +2148,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581280</v>
+        <v>581228</v>
       </c>
       <c r="R14" t="n">
-        <v>6509285</v>
+        <v>6509602</v>
       </c>
       <c r="S14" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2174,7 +2183,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2184,7 +2193,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2211,7 +2220,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119930938</v>
+        <v>119930937</v>
       </c>
       <c r="B15" t="n">
         <v>91884</v>
@@ -2246,7 +2255,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2254,14 +2263,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581280</v>
+        <v>581288</v>
       </c>
       <c r="R15" t="n">
-        <v>6509285</v>
+        <v>6509503</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2293,7 +2302,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2303,7 +2312,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2330,10 +2339,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119930949</v>
+        <v>119930894</v>
       </c>
       <c r="B16" t="n">
-        <v>94681</v>
+        <v>4772</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2346,41 +2355,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>102306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581228</v>
+        <v>581280</v>
       </c>
       <c r="R16" t="n">
-        <v>6509602</v>
+        <v>6509285</v>
       </c>
       <c r="S16" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2409,7 +2423,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2419,7 +2433,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2446,10 +2460,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119930937</v>
+        <v>119930907</v>
       </c>
       <c r="B17" t="n">
-        <v>91884</v>
+        <v>58166</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2458,25 +2472,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>208249</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2486,6 +2500,8 @@
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2493,10 +2509,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581288</v>
+        <v>581287</v>
       </c>
       <c r="R17" t="n">
-        <v>6509503</v>
+        <v>6509543</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2528,7 +2544,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2538,7 +2554,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2565,10 +2581,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119930905</v>
+        <v>119930933</v>
       </c>
       <c r="B18" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2577,50 +2593,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581280</v>
+        <v>581271</v>
       </c>
       <c r="R18" t="n">
-        <v>6509285</v>
+        <v>6509584</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2652,7 +2659,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2662,7 +2669,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2812,10 +2819,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119930900</v>
+        <v>119930949</v>
       </c>
       <c r="B20" t="n">
-        <v>5189</v>
+        <v>94681</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2828,32 +2835,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2867,7 +2869,7 @@
         <v>6509602</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2933,10 +2935,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119930894</v>
+        <v>119930913</v>
       </c>
       <c r="B21" t="n">
-        <v>4772</v>
+        <v>90966</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2949,43 +2951,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102306</v>
+        <v>5420</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581280</v>
+        <v>581228</v>
       </c>
       <c r="R21" t="n">
-        <v>6509285</v>
+        <v>6509602</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 37422-2024 artfynd.xlsx
+++ b/artfynd/A 37422-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119930953</v>
+        <v>119930894</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>4772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,28 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>102306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rökenskärr, Srm</t>
@@ -754,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119930929</v>
+        <v>119930907</v>
       </c>
       <c r="B3" t="n">
-        <v>91836</v>
+        <v>58166</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,26 +812,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4363</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581271</v>
+        <v>581287</v>
       </c>
       <c r="R3" t="n">
-        <v>6509584</v>
+        <v>6509543</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -869,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119930905</v>
+        <v>119930930</v>
       </c>
       <c r="B4" t="n">
-        <v>57463</v>
+        <v>91836</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,50 +929,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>4363</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581280</v>
+        <v>581271</v>
       </c>
       <c r="R4" t="n">
-        <v>6509285</v>
+        <v>6509584</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -993,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119930936</v>
+        <v>119930923</v>
       </c>
       <c r="B5" t="n">
-        <v>91863</v>
+        <v>91836</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,44 +1044,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4363</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581269</v>
+        <v>581280</v>
       </c>
       <c r="R5" t="n">
-        <v>6509448</v>
+        <v>6509285</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1118,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119930955</v>
+        <v>119930939</v>
       </c>
       <c r="B6" t="n">
-        <v>94681</v>
+        <v>91884</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,42 +1167,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581280</v>
+        <v>581163</v>
       </c>
       <c r="R6" t="n">
-        <v>6509285</v>
+        <v>6509559</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1224,7 +1237,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1247,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1381,10 +1394,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119930948</v>
+        <v>119930938</v>
       </c>
       <c r="B8" t="n">
-        <v>94681</v>
+        <v>91884</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,42 +1406,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581271</v>
+        <v>581280</v>
       </c>
       <c r="R8" t="n">
-        <v>6509584</v>
+        <v>6509285</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1460,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,7 +1486,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,10 +1513,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119930938</v>
+        <v>119930905</v>
       </c>
       <c r="B9" t="n">
-        <v>91884</v>
+        <v>57463</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1513,30 +1529,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1579,7 +1600,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,7 +1610,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,10 +1637,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119930952</v>
+        <v>119930946</v>
       </c>
       <c r="B10" t="n">
-        <v>96865</v>
+        <v>94681</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,29 +1653,25 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221946</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1664,10 +1681,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581256</v>
+        <v>581271</v>
       </c>
       <c r="R10" t="n">
-        <v>6509395</v>
+        <v>6509584</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1699,7 +1716,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1709,7 +1726,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,10 +1753,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119930944</v>
+        <v>119930936</v>
       </c>
       <c r="B11" t="n">
-        <v>94681</v>
+        <v>91863</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,35 +1765,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1784,13 +1796,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581299</v>
+        <v>581269</v>
       </c>
       <c r="R11" t="n">
-        <v>6509583</v>
+        <v>6509448</v>
       </c>
       <c r="S11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1819,7 +1831,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1829,12 +1841,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2 kuddar</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1861,10 +1868,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119930921</v>
+        <v>119930937</v>
       </c>
       <c r="B12" t="n">
-        <v>91185</v>
+        <v>91884</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1873,25 +1880,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6031</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1908,13 +1915,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581280</v>
+        <v>581288</v>
       </c>
       <c r="R12" t="n">
-        <v>6509285</v>
+        <v>6509503</v>
       </c>
       <c r="S12" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1943,7 +1950,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1953,7 +1960,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1980,10 +1987,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119930939</v>
+        <v>119930944</v>
       </c>
       <c r="B13" t="n">
-        <v>91884</v>
+        <v>94681</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1992,34 +1999,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2027,13 +2035,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581163</v>
+        <v>581299</v>
       </c>
       <c r="R13" t="n">
-        <v>6509559</v>
+        <v>6509583</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2062,7 +2070,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2072,7 +2080,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2 kuddar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2099,10 +2112,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119930900</v>
+        <v>119930953</v>
       </c>
       <c r="B14" t="n">
-        <v>5189</v>
+        <v>91840</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2115,43 +2128,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>51</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581228</v>
+        <v>581280</v>
       </c>
       <c r="R14" t="n">
-        <v>6509602</v>
+        <v>6509285</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2183,7 +2191,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2193,7 +2201,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2220,10 +2228,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119930937</v>
+        <v>119930952</v>
       </c>
       <c r="B15" t="n">
-        <v>91884</v>
+        <v>96865</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2232,34 +2240,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5449</v>
+        <v>221946</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2267,10 +2276,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581288</v>
+        <v>581256</v>
       </c>
       <c r="R15" t="n">
-        <v>6509503</v>
+        <v>6509395</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2302,7 +2311,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2312,7 +2321,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2339,10 +2348,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119930894</v>
+        <v>119930949</v>
       </c>
       <c r="B16" t="n">
-        <v>4772</v>
+        <v>94681</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2355,46 +2364,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102306</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581280</v>
+        <v>581228</v>
       </c>
       <c r="R16" t="n">
-        <v>6509285</v>
+        <v>6509602</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2423,7 +2427,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2433,7 +2437,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2460,10 +2464,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119930907</v>
+        <v>119930900</v>
       </c>
       <c r="B17" t="n">
-        <v>58166</v>
+        <v>5189</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2476,21 +2480,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>208249</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2509,10 +2513,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581287</v>
+        <v>581228</v>
       </c>
       <c r="R17" t="n">
-        <v>6509543</v>
+        <v>6509602</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2544,7 +2548,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2554,7 +2558,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2581,10 +2585,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119930933</v>
+        <v>119930921</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
+        <v>91185</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2597,24 +2601,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2624,13 +2632,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581271</v>
+        <v>581280</v>
       </c>
       <c r="R18" t="n">
-        <v>6509584</v>
+        <v>6509285</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2659,7 +2667,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2669,7 +2677,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2696,10 +2704,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119930923</v>
+        <v>119930913</v>
       </c>
       <c r="B19" t="n">
-        <v>91836</v>
+        <v>90966</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2712,28 +2720,24 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4363</v>
+        <v>5420</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -2743,14 +2747,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581280</v>
+        <v>581228</v>
       </c>
       <c r="R19" t="n">
-        <v>6509285</v>
+        <v>6509602</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2782,7 +2786,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2792,7 +2796,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2819,7 +2823,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119930949</v>
+        <v>119930955</v>
       </c>
       <c r="B20" t="n">
         <v>94681</v>
@@ -2852,24 +2856,24 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581228</v>
+        <v>581280</v>
       </c>
       <c r="R20" t="n">
-        <v>6509602</v>
+        <v>6509285</v>
       </c>
       <c r="S20" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2898,7 +2902,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2908,7 +2912,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2935,10 +2939,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119930913</v>
+        <v>119930933</v>
       </c>
       <c r="B21" t="n">
-        <v>90966</v>
+        <v>91840</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2951,29 +2955,25 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581228</v>
+        <v>581271</v>
       </c>
       <c r="R21" t="n">
-        <v>6509602</v>
+        <v>6509584</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 37422-2024 artfynd.xlsx
+++ b/artfynd/A 37422-2024 artfynd.xlsx
@@ -1637,10 +1637,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119930946</v>
+        <v>119930936</v>
       </c>
       <c r="B10" t="n">
-        <v>94681</v>
+        <v>91863</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1649,31 +1649,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1681,13 +1680,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581271</v>
+        <v>581269</v>
       </c>
       <c r="R10" t="n">
-        <v>6509584</v>
+        <v>6509448</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1716,7 +1715,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1726,7 +1725,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1753,10 +1752,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119930936</v>
+        <v>119930946</v>
       </c>
       <c r="B11" t="n">
-        <v>91863</v>
+        <v>94681</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1765,30 +1764,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1796,13 +1796,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581269</v>
+        <v>581271</v>
       </c>
       <c r="R11" t="n">
-        <v>6509448</v>
+        <v>6509584</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2585,10 +2585,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119930921</v>
+        <v>119930933</v>
       </c>
       <c r="B18" t="n">
-        <v>91185</v>
+        <v>91840</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2601,28 +2601,24 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2632,13 +2628,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581280</v>
+        <v>581271</v>
       </c>
       <c r="R18" t="n">
-        <v>6509285</v>
+        <v>6509584</v>
       </c>
       <c r="S18" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2667,7 +2663,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2677,7 +2673,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2939,10 +2935,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119930933</v>
+        <v>119930921</v>
       </c>
       <c r="B21" t="n">
-        <v>91840</v>
+        <v>91185</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2955,24 +2951,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -2982,13 +2982,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581271</v>
+        <v>581280</v>
       </c>
       <c r="R21" t="n">
-        <v>6509584</v>
+        <v>6509285</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 37422-2024 artfynd.xlsx
+++ b/artfynd/A 37422-2024 artfynd.xlsx
@@ -2112,10 +2112,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119930953</v>
+        <v>119930952</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
+        <v>96865</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2128,38 +2128,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>221946</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581280</v>
+        <v>581256</v>
       </c>
       <c r="R14" t="n">
-        <v>6509285</v>
+        <v>6509395</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2191,7 +2195,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2201,7 +2205,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2228,10 +2232,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119930952</v>
+        <v>119930953</v>
       </c>
       <c r="B15" t="n">
-        <v>96865</v>
+        <v>91840</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2244,42 +2248,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221946</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581256</v>
+        <v>581280</v>
       </c>
       <c r="R15" t="n">
-        <v>6509395</v>
+        <v>6509285</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2585,10 +2585,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119930933</v>
+        <v>119930921</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
+        <v>91185</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2601,24 +2601,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2628,13 +2632,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581271</v>
+        <v>581280</v>
       </c>
       <c r="R18" t="n">
-        <v>6509584</v>
+        <v>6509285</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2663,7 +2667,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2673,7 +2677,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2935,10 +2939,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119930921</v>
+        <v>119930933</v>
       </c>
       <c r="B21" t="n">
-        <v>91185</v>
+        <v>91840</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2951,28 +2955,24 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -2982,13 +2982,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581280</v>
+        <v>581271</v>
       </c>
       <c r="R21" t="n">
-        <v>6509285</v>
+        <v>6509584</v>
       </c>
       <c r="S21" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 37422-2024 artfynd.xlsx
+++ b/artfynd/A 37422-2024 artfynd.xlsx
@@ -2112,10 +2112,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119930952</v>
+        <v>119930953</v>
       </c>
       <c r="B14" t="n">
-        <v>96865</v>
+        <v>91840</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2128,42 +2128,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221946</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581256</v>
+        <v>581280</v>
       </c>
       <c r="R14" t="n">
-        <v>6509395</v>
+        <v>6509285</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2195,7 +2191,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2205,7 +2201,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2232,10 +2228,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119930953</v>
+        <v>119930952</v>
       </c>
       <c r="B15" t="n">
-        <v>91840</v>
+        <v>96865</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2248,38 +2244,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>221946</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581280</v>
+        <v>581256</v>
       </c>
       <c r="R15" t="n">
-        <v>6509285</v>
+        <v>6509395</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 37422-2024 artfynd.xlsx
+++ b/artfynd/A 37422-2024 artfynd.xlsx
@@ -1637,10 +1637,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119930936</v>
+        <v>119930946</v>
       </c>
       <c r="B10" t="n">
-        <v>91863</v>
+        <v>94681</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1649,30 +1649,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1680,13 +1681,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581269</v>
+        <v>581271</v>
       </c>
       <c r="R10" t="n">
-        <v>6509448</v>
+        <v>6509584</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1715,7 +1716,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1725,7 +1726,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1752,10 +1753,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119930946</v>
+        <v>119930936</v>
       </c>
       <c r="B11" t="n">
-        <v>94681</v>
+        <v>91863</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,31 +1765,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1796,13 +1796,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581271</v>
+        <v>581269</v>
       </c>
       <c r="R11" t="n">
-        <v>6509584</v>
+        <v>6509448</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 37422-2024 artfynd.xlsx
+++ b/artfynd/A 37422-2024 artfynd.xlsx
@@ -1637,10 +1637,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119930946</v>
+        <v>119930936</v>
       </c>
       <c r="B10" t="n">
-        <v>94681</v>
+        <v>91863</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1649,31 +1649,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1681,13 +1680,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581271</v>
+        <v>581269</v>
       </c>
       <c r="R10" t="n">
-        <v>6509584</v>
+        <v>6509448</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1716,7 +1715,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1726,7 +1725,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1753,10 +1752,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119930936</v>
+        <v>119930946</v>
       </c>
       <c r="B11" t="n">
-        <v>91863</v>
+        <v>94681</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1765,30 +1764,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1796,13 +1796,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581269</v>
+        <v>581271</v>
       </c>
       <c r="R11" t="n">
-        <v>6509448</v>
+        <v>6509584</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 37422-2024 artfynd.xlsx
+++ b/artfynd/A 37422-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119930894</v>
+        <v>119930953</v>
       </c>
       <c r="B2" t="n">
-        <v>4772</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102306</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>51</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rökenskärr, Srm</t>
@@ -759,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119930907</v>
+        <v>119930949</v>
       </c>
       <c r="B3" t="n">
-        <v>58166</v>
+        <v>94704</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,32 +807,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -845,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581287</v>
+        <v>581228</v>
       </c>
       <c r="R3" t="n">
-        <v>6509543</v>
+        <v>6509602</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119930930</v>
+        <v>119930944</v>
       </c>
       <c r="B4" t="n">
-        <v>91836</v>
+        <v>94704</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,26 +923,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4363</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -960,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581271</v>
+        <v>581299</v>
       </c>
       <c r="R4" t="n">
-        <v>6509584</v>
+        <v>6509583</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1000,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2 kuddar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119930923</v>
+        <v>119930907</v>
       </c>
       <c r="B5" t="n">
-        <v>91836</v>
+        <v>58176</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,45 +1048,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4363</v>
+        <v>208249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581280</v>
+        <v>581287</v>
       </c>
       <c r="R5" t="n">
-        <v>6509285</v>
+        <v>6509543</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1118,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119930939</v>
+        <v>119930952</v>
       </c>
       <c r="B6" t="n">
-        <v>91884</v>
+        <v>96888</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,34 +1165,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>221946</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1202,10 +1201,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581163</v>
+        <v>581256</v>
       </c>
       <c r="R6" t="n">
-        <v>6509559</v>
+        <v>6509395</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1237,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,7 +1246,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119930945</v>
+        <v>119930936</v>
       </c>
       <c r="B7" t="n">
-        <v>94681</v>
+        <v>91881</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,35 +1285,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1322,13 +1316,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581292</v>
+        <v>581269</v>
       </c>
       <c r="R7" t="n">
-        <v>6509594</v>
+        <v>6509448</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1357,7 +1351,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1367,7 +1361,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,10 +1388,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119930938</v>
+        <v>119930937</v>
       </c>
       <c r="B8" t="n">
-        <v>91884</v>
+        <v>91902</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1429,7 +1423,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1437,14 +1431,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581280</v>
+        <v>581288</v>
       </c>
       <c r="R8" t="n">
-        <v>6509285</v>
+        <v>6509503</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1476,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1480,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,10 +1507,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119930905</v>
+        <v>119930930</v>
       </c>
       <c r="B9" t="n">
-        <v>57463</v>
+        <v>91854</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,50 +1519,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>4363</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581280</v>
+        <v>581271</v>
       </c>
       <c r="R9" t="n">
-        <v>6509285</v>
+        <v>6509584</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1600,7 +1585,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1610,7 +1595,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1637,10 +1622,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119930936</v>
+        <v>119930946</v>
       </c>
       <c r="B10" t="n">
-        <v>91863</v>
+        <v>94704</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1649,30 +1634,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1680,13 +1666,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581269</v>
+        <v>581271</v>
       </c>
       <c r="R10" t="n">
-        <v>6509448</v>
+        <v>6509584</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1715,7 +1701,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1725,7 +1711,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1752,10 +1738,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119930946</v>
+        <v>119930900</v>
       </c>
       <c r="B11" t="n">
-        <v>94681</v>
+        <v>5189</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1768,27 +1754,32 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1796,10 +1787,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581271</v>
+        <v>581228</v>
       </c>
       <c r="R11" t="n">
-        <v>6509584</v>
+        <v>6509602</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1831,7 +1822,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1841,7 +1832,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1868,10 +1859,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119930937</v>
+        <v>119930913</v>
       </c>
       <c r="B12" t="n">
-        <v>91884</v>
+        <v>90984</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1880,33 +1871,33 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>5420</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1915,10 +1906,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581288</v>
+        <v>581228</v>
       </c>
       <c r="R12" t="n">
-        <v>6509503</v>
+        <v>6509602</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1950,7 +1941,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1960,7 +1951,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,10 +1978,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119930944</v>
+        <v>119930923</v>
       </c>
       <c r="B13" t="n">
-        <v>94681</v>
+        <v>91854</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2003,45 +1994,48 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>4363</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581299</v>
+        <v>581280</v>
       </c>
       <c r="R13" t="n">
-        <v>6509583</v>
+        <v>6509285</v>
       </c>
       <c r="S13" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2070,7 +2064,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2080,12 +2074,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2 kuddar</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2112,10 +2101,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119930953</v>
+        <v>119930894</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
+        <v>4772</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2128,28 +2117,33 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>102306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rökenskärr, Srm</t>
@@ -2191,7 +2185,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2201,7 +2195,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2228,10 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119930952</v>
+        <v>119930955</v>
       </c>
       <c r="B15" t="n">
-        <v>96865</v>
+        <v>94704</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2244,42 +2238,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221946</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581256</v>
+        <v>581280</v>
       </c>
       <c r="R15" t="n">
-        <v>6509395</v>
+        <v>6509285</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2311,7 +2301,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2321,7 +2311,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2348,10 +2338,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119930949</v>
+        <v>119930939</v>
       </c>
       <c r="B16" t="n">
-        <v>94681</v>
+        <v>91902</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2360,31 +2350,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2392,13 +2385,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581228</v>
+        <v>581163</v>
       </c>
       <c r="R16" t="n">
-        <v>6509602</v>
+        <v>6509559</v>
       </c>
       <c r="S16" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2427,7 +2420,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2437,7 +2430,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2464,10 +2457,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119930900</v>
+        <v>119930905</v>
       </c>
       <c r="B17" t="n">
-        <v>5189</v>
+        <v>57473</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2476,25 +2469,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2502,21 +2495,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581228</v>
+        <v>581280</v>
       </c>
       <c r="R17" t="n">
-        <v>6509602</v>
+        <v>6509285</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2548,7 +2544,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2558,7 +2554,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2588,7 +2584,7 @@
         <v>119930921</v>
       </c>
       <c r="B18" t="n">
-        <v>91185</v>
+        <v>91203</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2704,10 +2700,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119930913</v>
+        <v>119930938</v>
       </c>
       <c r="B19" t="n">
-        <v>90966</v>
+        <v>91902</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2716,45 +2712,45 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5420</v>
+        <v>5449</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581228</v>
+        <v>581280</v>
       </c>
       <c r="R19" t="n">
-        <v>6509602</v>
+        <v>6509285</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2786,7 +2782,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2796,7 +2792,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2823,10 +2819,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119930955</v>
+        <v>119930945</v>
       </c>
       <c r="B20" t="n">
-        <v>94681</v>
+        <v>94704</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2858,22 +2854,26 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581280</v>
+        <v>581292</v>
       </c>
       <c r="R20" t="n">
-        <v>6509285</v>
+        <v>6509594</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2942,7 +2942,7 @@
         <v>119930933</v>
       </c>
       <c r="B21" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 37422-2024 artfynd.xlsx
+++ b/artfynd/A 37422-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119930953</v>
+        <v>119930944</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
+        <v>94704</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,41 +691,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581280</v>
+        <v>581299</v>
       </c>
       <c r="R2" t="n">
-        <v>6509285</v>
+        <v>6509583</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +768,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2 kuddar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119930949</v>
+        <v>119930937</v>
       </c>
       <c r="B3" t="n">
-        <v>94704</v>
+        <v>91902</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,31 +812,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581228</v>
+        <v>581288</v>
       </c>
       <c r="R3" t="n">
-        <v>6509602</v>
+        <v>6509503</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119930944</v>
+        <v>119930930</v>
       </c>
       <c r="B4" t="n">
-        <v>94704</v>
+        <v>91854</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,31 +935,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>4363</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,13 +962,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581299</v>
+        <v>581271</v>
       </c>
       <c r="R4" t="n">
-        <v>6509583</v>
+        <v>6509584</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,12 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2 kuddar</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119930907</v>
+        <v>119930905</v>
       </c>
       <c r="B5" t="n">
-        <v>58176</v>
+        <v>57473</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,25 +1046,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208249</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1070,21 +1072,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581287</v>
+        <v>581280</v>
       </c>
       <c r="R5" t="n">
-        <v>6509543</v>
+        <v>6509285</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1116,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1131,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119930952</v>
+        <v>119930894</v>
       </c>
       <c r="B6" t="n">
-        <v>96888</v>
+        <v>4772</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,42 +1174,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>102306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581256</v>
+        <v>581280</v>
       </c>
       <c r="R6" t="n">
-        <v>6509395</v>
+        <v>6509285</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1236,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,7 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,10 +1279,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119930936</v>
+        <v>119930952</v>
       </c>
       <c r="B7" t="n">
-        <v>91881</v>
+        <v>96888</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,30 +1291,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>221946</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1316,13 +1327,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581269</v>
+        <v>581256</v>
       </c>
       <c r="R7" t="n">
-        <v>6509448</v>
+        <v>6509395</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1351,7 +1362,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1361,7 +1372,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1388,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119930937</v>
+        <v>119930946</v>
       </c>
       <c r="B8" t="n">
-        <v>91902</v>
+        <v>94704</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1400,34 +1411,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1435,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581288</v>
+        <v>581271</v>
       </c>
       <c r="R8" t="n">
-        <v>6509503</v>
+        <v>6509584</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1470,7 +1478,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,7 +1488,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,10 +1515,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119930930</v>
+        <v>119930933</v>
       </c>
       <c r="B9" t="n">
-        <v>91854</v>
+        <v>91858</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1523,21 +1531,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4363</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1585,7 +1593,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1595,7 +1603,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1622,10 +1630,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119930946</v>
+        <v>119930953</v>
       </c>
       <c r="B10" t="n">
-        <v>94704</v>
+        <v>91858</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1638,38 +1646,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581271</v>
+        <v>581280</v>
       </c>
       <c r="R10" t="n">
-        <v>6509584</v>
+        <v>6509285</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1701,7 +1709,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1711,7 +1719,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1738,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119930900</v>
+        <v>119930907</v>
       </c>
       <c r="B11" t="n">
-        <v>5189</v>
+        <v>58176</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,21 +1762,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>208249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1787,10 +1795,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581228</v>
+        <v>581287</v>
       </c>
       <c r="R11" t="n">
-        <v>6509602</v>
+        <v>6509543</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1822,7 +1830,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1832,7 +1840,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1859,10 +1867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119930913</v>
+        <v>119930945</v>
       </c>
       <c r="B12" t="n">
-        <v>90984</v>
+        <v>94704</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1875,30 +1883,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1906,13 +1915,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581228</v>
+        <v>581292</v>
       </c>
       <c r="R12" t="n">
-        <v>6509602</v>
+        <v>6509594</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1941,7 +1950,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1951,7 +1960,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2101,10 +2110,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119930894</v>
+        <v>119930913</v>
       </c>
       <c r="B14" t="n">
-        <v>4772</v>
+        <v>90984</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2117,43 +2126,41 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102306</v>
+        <v>5420</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581280</v>
+        <v>581228</v>
       </c>
       <c r="R14" t="n">
-        <v>6509285</v>
+        <v>6509602</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2185,7 +2192,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2195,7 +2202,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2222,10 +2229,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119930955</v>
+        <v>119930900</v>
       </c>
       <c r="B15" t="n">
-        <v>94704</v>
+        <v>5189</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2238,38 +2245,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581280</v>
+        <v>581228</v>
       </c>
       <c r="R15" t="n">
-        <v>6509285</v>
+        <v>6509602</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2301,7 +2313,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2311,7 +2323,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2338,10 +2350,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119930939</v>
+        <v>119930949</v>
       </c>
       <c r="B16" t="n">
-        <v>91902</v>
+        <v>94704</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2350,34 +2362,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2385,13 +2394,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581163</v>
+        <v>581228</v>
       </c>
       <c r="R16" t="n">
-        <v>6509559</v>
+        <v>6509602</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2420,7 +2429,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2430,7 +2439,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2457,10 +2466,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119930905</v>
+        <v>119930938</v>
       </c>
       <c r="B17" t="n">
-        <v>57473</v>
+        <v>91902</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2473,35 +2482,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>5449</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2544,7 +2548,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2554,7 +2558,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2700,7 +2704,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119930938</v>
+        <v>119930939</v>
       </c>
       <c r="B19" t="n">
         <v>91902</v>
@@ -2735,7 +2739,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2743,14 +2747,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581280</v>
+        <v>581163</v>
       </c>
       <c r="R19" t="n">
-        <v>6509285</v>
+        <v>6509559</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2782,7 +2786,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2792,7 +2796,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2819,10 +2823,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119930945</v>
+        <v>119930936</v>
       </c>
       <c r="B20" t="n">
-        <v>94704</v>
+        <v>91881</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2831,35 +2835,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2867,13 +2866,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581292</v>
+        <v>581269</v>
       </c>
       <c r="R20" t="n">
-        <v>6509594</v>
+        <v>6509448</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2902,7 +2901,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2912,7 +2911,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2939,10 +2938,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119930933</v>
+        <v>119930955</v>
       </c>
       <c r="B21" t="n">
-        <v>91858</v>
+        <v>94704</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2955,37 +2954,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581271</v>
+        <v>581280</v>
       </c>
       <c r="R21" t="n">
-        <v>6509584</v>
+        <v>6509285</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 37422-2024 artfynd.xlsx
+++ b/artfynd/A 37422-2024 artfynd.xlsx
@@ -2110,10 +2110,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119930913</v>
+        <v>119930900</v>
       </c>
       <c r="B14" t="n">
-        <v>90984</v>
+        <v>5189</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2126,30 +2126,32 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5420</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2192,7 +2194,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2202,7 +2204,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2229,10 +2231,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119930900</v>
+        <v>119930913</v>
       </c>
       <c r="B15" t="n">
-        <v>5189</v>
+        <v>90984</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2245,32 +2247,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>5420</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 37422-2024 artfynd.xlsx
+++ b/artfynd/A 37422-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119930937</v>
+        <v>119930933</v>
       </c>
       <c r="B3" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,32 +812,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -847,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581288</v>
+        <v>581271</v>
       </c>
       <c r="R3" t="n">
-        <v>6509503</v>
+        <v>6509584</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -882,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119930930</v>
+        <v>119930929</v>
       </c>
       <c r="B4" t="n">
         <v>91854</v>
@@ -997,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119930905</v>
+        <v>119930938</v>
       </c>
       <c r="B5" t="n">
-        <v>57473</v>
+        <v>91902</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,35 +1046,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1121,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1279,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119930952</v>
+        <v>119930950</v>
       </c>
       <c r="B7" t="n">
-        <v>96888</v>
+        <v>91858</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,42 +1286,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221946</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581256</v>
+        <v>581280</v>
       </c>
       <c r="R7" t="n">
-        <v>6509395</v>
+        <v>6509285</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1362,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1372,7 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119930946</v>
+        <v>119930907</v>
       </c>
       <c r="B8" t="n">
-        <v>94704</v>
+        <v>58176</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1415,27 +1402,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>208249</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1443,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581271</v>
+        <v>581287</v>
       </c>
       <c r="R8" t="n">
-        <v>6509584</v>
+        <v>6509543</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1478,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1488,7 +1480,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,10 +1507,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119930933</v>
+        <v>119930946</v>
       </c>
       <c r="B9" t="n">
-        <v>91858</v>
+        <v>94704</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1531,26 +1523,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1593,7 +1586,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1603,7 +1596,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1630,10 +1623,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119930953</v>
+        <v>119930945</v>
       </c>
       <c r="B10" t="n">
-        <v>91858</v>
+        <v>94704</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1646,41 +1639,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581280</v>
+        <v>581292</v>
       </c>
       <c r="R10" t="n">
-        <v>6509285</v>
+        <v>6509594</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1709,7 +1706,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1719,7 +1716,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1746,10 +1743,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119930907</v>
+        <v>119930955</v>
       </c>
       <c r="B11" t="n">
-        <v>58176</v>
+        <v>94704</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1762,43 +1759,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208249</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581287</v>
+        <v>581280</v>
       </c>
       <c r="R11" t="n">
-        <v>6509543</v>
+        <v>6509285</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1830,7 +1822,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1840,7 +1832,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1867,7 +1859,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119930945</v>
+        <v>119930949</v>
       </c>
       <c r="B12" t="n">
         <v>94704</v>
@@ -1900,11 +1892,7 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1915,13 +1903,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581292</v>
+        <v>581228</v>
       </c>
       <c r="R12" t="n">
-        <v>6509594</v>
+        <v>6509602</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1950,7 +1938,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1960,7 +1948,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,10 +1975,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119930923</v>
+        <v>119930921</v>
       </c>
       <c r="B13" t="n">
-        <v>91854</v>
+        <v>91203</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2003,38 +1991,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4363</v>
+        <v>6031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
@@ -2044,7 +2028,7 @@
         <v>6509285</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2073,7 +2057,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2083,7 +2067,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2110,10 +2094,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119930900</v>
+        <v>119930905</v>
       </c>
       <c r="B14" t="n">
-        <v>5189</v>
+        <v>57473</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2122,25 +2106,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2148,21 +2132,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581228</v>
+        <v>581280</v>
       </c>
       <c r="R14" t="n">
-        <v>6509602</v>
+        <v>6509285</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2194,7 +2181,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2204,7 +2191,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2231,10 +2218,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119930913</v>
+        <v>119930952</v>
       </c>
       <c r="B15" t="n">
-        <v>90984</v>
+        <v>96888</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2247,30 +2234,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5420</v>
+        <v>221946</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2278,10 +2266,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581228</v>
+        <v>581256</v>
       </c>
       <c r="R15" t="n">
-        <v>6509602</v>
+        <v>6509395</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2313,7 +2301,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2323,7 +2311,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2350,10 +2338,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119930949</v>
+        <v>119930900</v>
       </c>
       <c r="B16" t="n">
-        <v>94704</v>
+        <v>5189</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2366,27 +2354,32 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>105930</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2400,7 +2393,7 @@
         <v>6509602</v>
       </c>
       <c r="S16" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2466,10 +2459,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119930938</v>
+        <v>119930923</v>
       </c>
       <c r="B17" t="n">
-        <v>91902</v>
+        <v>91854</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2478,33 +2471,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>4363</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2548,7 +2545,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2558,7 +2555,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2585,10 +2582,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119930921</v>
+        <v>119930937</v>
       </c>
       <c r="B18" t="n">
-        <v>91203</v>
+        <v>91902</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2597,25 +2594,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6031</v>
+        <v>5449</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2632,13 +2629,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581280</v>
+        <v>581288</v>
       </c>
       <c r="R18" t="n">
-        <v>6509285</v>
+        <v>6509503</v>
       </c>
       <c r="S18" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2667,7 +2664,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2677,7 +2674,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2704,10 +2701,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119930939</v>
+        <v>119930913</v>
       </c>
       <c r="B19" t="n">
-        <v>91902</v>
+        <v>90984</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2716,33 +2713,33 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5449</v>
+        <v>5420</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2751,10 +2748,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581163</v>
+        <v>581228</v>
       </c>
       <c r="R19" t="n">
-        <v>6509559</v>
+        <v>6509602</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2786,7 +2783,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2796,7 +2793,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2938,10 +2935,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119930955</v>
+        <v>119930939</v>
       </c>
       <c r="B21" t="n">
-        <v>94704</v>
+        <v>91902</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2950,42 +2947,45 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581280</v>
+        <v>581163</v>
       </c>
       <c r="R21" t="n">
-        <v>6509285</v>
+        <v>6509559</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 37422-2024 artfynd.xlsx
+++ b/artfynd/A 37422-2024 artfynd.xlsx
@@ -1386,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119930907</v>
+        <v>119930946</v>
       </c>
       <c r="B8" t="n">
-        <v>58176</v>
+        <v>94704</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,32 +1402,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208249</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1435,10 +1430,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581287</v>
+        <v>581271</v>
       </c>
       <c r="R8" t="n">
-        <v>6509543</v>
+        <v>6509584</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1470,7 +1465,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,7 +1475,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,7 +1502,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119930946</v>
+        <v>119930945</v>
       </c>
       <c r="B9" t="n">
         <v>94704</v>
@@ -1540,7 +1535,11 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -1551,13 +1550,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581271</v>
+        <v>581292</v>
       </c>
       <c r="R9" t="n">
-        <v>6509584</v>
+        <v>6509594</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1586,7 +1585,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1596,7 +1595,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1623,7 +1622,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119930945</v>
+        <v>119930955</v>
       </c>
       <c r="B10" t="n">
         <v>94704</v>
@@ -1658,26 +1657,22 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581292</v>
+        <v>581280</v>
       </c>
       <c r="R10" t="n">
-        <v>6509594</v>
+        <v>6509285</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1706,7 +1701,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1716,7 +1711,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1743,10 +1738,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119930955</v>
+        <v>119930907</v>
       </c>
       <c r="B11" t="n">
-        <v>94704</v>
+        <v>58176</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1759,38 +1754,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>208249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581280</v>
+        <v>581287</v>
       </c>
       <c r="R11" t="n">
-        <v>6509285</v>
+        <v>6509543</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 37422-2024 artfynd.xlsx
+++ b/artfynd/A 37422-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119930944</v>
+        <v>119930938</v>
       </c>
       <c r="B2" t="n">
-        <v>94704</v>
+        <v>91902</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,49 +687,48 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581299</v>
+        <v>581280</v>
       </c>
       <c r="R2" t="n">
-        <v>6509583</v>
+        <v>6509285</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,12 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2 kuddar</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119930933</v>
+        <v>119930930</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>91854</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -878,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119930929</v>
+        <v>119930937</v>
       </c>
       <c r="B4" t="n">
-        <v>91854</v>
+        <v>91902</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,28 +921,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4363</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -958,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581271</v>
+        <v>581288</v>
       </c>
       <c r="R4" t="n">
-        <v>6509584</v>
+        <v>6509503</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -993,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119930938</v>
+        <v>119930948</v>
       </c>
       <c r="B5" t="n">
-        <v>91902</v>
+        <v>94704</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,45 +1040,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581280</v>
+        <v>581271</v>
       </c>
       <c r="R5" t="n">
-        <v>6509285</v>
+        <v>6509584</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1112,7 +1107,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1117,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1270,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119930950</v>
+        <v>119930949</v>
       </c>
       <c r="B7" t="n">
-        <v>91858</v>
+        <v>94704</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,41 +1281,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581280</v>
+        <v>581228</v>
       </c>
       <c r="R7" t="n">
-        <v>6509285</v>
+        <v>6509602</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1349,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119930946</v>
+        <v>119930913</v>
       </c>
       <c r="B8" t="n">
-        <v>94704</v>
+        <v>90984</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,27 +1397,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1430,10 +1428,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581271</v>
+        <v>581228</v>
       </c>
       <c r="R8" t="n">
-        <v>6509584</v>
+        <v>6509602</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1465,7 +1463,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1475,7 +1473,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,10 +1500,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119930945</v>
+        <v>119930900</v>
       </c>
       <c r="B9" t="n">
-        <v>94704</v>
+        <v>5189</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,21 +1516,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1543,6 +1541,7 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1550,13 +1549,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581292</v>
+        <v>581228</v>
       </c>
       <c r="R9" t="n">
-        <v>6509594</v>
+        <v>6509602</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1585,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1595,7 +1594,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1622,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119930955</v>
+        <v>119930939</v>
       </c>
       <c r="B10" t="n">
-        <v>94704</v>
+        <v>91902</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1634,42 +1633,45 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581280</v>
+        <v>581163</v>
       </c>
       <c r="R10" t="n">
-        <v>6509285</v>
+        <v>6509559</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1701,7 +1703,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1711,7 +1713,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1738,10 +1740,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119930907</v>
+        <v>119930944</v>
       </c>
       <c r="B11" t="n">
-        <v>58176</v>
+        <v>94704</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,32 +1756,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208249</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1787,13 +1788,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581287</v>
+        <v>581299</v>
       </c>
       <c r="R11" t="n">
-        <v>6509543</v>
+        <v>6509583</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1822,7 +1823,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1832,7 +1833,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2 kuddar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1859,10 +1865,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119930949</v>
+        <v>119930921</v>
       </c>
       <c r="B12" t="n">
-        <v>94704</v>
+        <v>91203</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1875,27 +1881,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>6031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1903,13 +1912,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581228</v>
+        <v>581280</v>
       </c>
       <c r="R12" t="n">
-        <v>6509602</v>
+        <v>6509285</v>
       </c>
       <c r="S12" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1938,7 +1947,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1948,7 +1957,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1975,10 +1984,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119930921</v>
+        <v>119930950</v>
       </c>
       <c r="B13" t="n">
-        <v>91203</v>
+        <v>91858</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1991,34 +2000,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
@@ -2028,7 +2034,7 @@
         <v>6509285</v>
       </c>
       <c r="S13" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2057,7 +2063,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2067,7 +2073,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2094,10 +2100,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119930905</v>
+        <v>119930945</v>
       </c>
       <c r="B14" t="n">
-        <v>57473</v>
+        <v>94704</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2106,25 +2112,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2132,27 +2138,23 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581280</v>
+        <v>581292</v>
       </c>
       <c r="R14" t="n">
-        <v>6509285</v>
+        <v>6509594</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2181,7 +2183,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2191,7 +2193,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2218,10 +2220,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119930952</v>
+        <v>119930907</v>
       </c>
       <c r="B15" t="n">
-        <v>96888</v>
+        <v>58176</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2234,31 +2236,32 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221946</v>
+        <v>208249</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2266,10 +2269,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581256</v>
+        <v>581287</v>
       </c>
       <c r="R15" t="n">
-        <v>6509395</v>
+        <v>6509543</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2301,7 +2304,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2311,7 +2314,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2338,10 +2341,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119930900</v>
+        <v>119930952</v>
       </c>
       <c r="B16" t="n">
-        <v>5189</v>
+        <v>96888</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2354,32 +2357,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>221946</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2387,10 +2389,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581228</v>
+        <v>581256</v>
       </c>
       <c r="R16" t="n">
-        <v>6509602</v>
+        <v>6509395</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2422,7 +2424,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2432,7 +2434,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2459,10 +2461,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119930923</v>
+        <v>119930955</v>
       </c>
       <c r="B17" t="n">
-        <v>91854</v>
+        <v>94704</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2475,35 +2477,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4363</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rökenskärr, Srm</t>
@@ -2545,7 +2540,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2555,7 +2550,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2582,10 +2577,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119930937</v>
+        <v>119930905</v>
       </c>
       <c r="B18" t="n">
-        <v>91902</v>
+        <v>57473</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2598,21 +2593,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2620,19 +2615,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581288</v>
+        <v>581280</v>
       </c>
       <c r="R18" t="n">
-        <v>6509503</v>
+        <v>6509285</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2701,10 +2701,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119930913</v>
+        <v>119930936</v>
       </c>
       <c r="B19" t="n">
-        <v>90984</v>
+        <v>91881</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2713,33 +2713,29 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5420</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2748,13 +2744,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581228</v>
+        <v>581269</v>
       </c>
       <c r="R19" t="n">
-        <v>6509602</v>
+        <v>6509448</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2783,7 +2779,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2793,7 +2789,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2820,10 +2816,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119930936</v>
+        <v>119930923</v>
       </c>
       <c r="B20" t="n">
-        <v>91881</v>
+        <v>91854</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2832,44 +2828,52 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>4363</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581269</v>
+        <v>581280</v>
       </c>
       <c r="R20" t="n">
-        <v>6509448</v>
+        <v>6509285</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2898,7 +2902,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2908,7 +2912,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2935,10 +2939,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119930939</v>
+        <v>119930933</v>
       </c>
       <c r="B21" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2947,32 +2951,28 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581163</v>
+        <v>581271</v>
       </c>
       <c r="R21" t="n">
-        <v>6509559</v>
+        <v>6509584</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 37422-2024 artfynd.xlsx
+++ b/artfynd/A 37422-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119930938</v>
+        <v>119930939</v>
       </c>
       <c r="B2" t="n">
         <v>91902</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -718,14 +718,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581280</v>
+        <v>581163</v>
       </c>
       <c r="R2" t="n">
-        <v>6509285</v>
+        <v>6509559</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119930930</v>
+        <v>119930913</v>
       </c>
       <c r="B3" t="n">
-        <v>91854</v>
+        <v>90984</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,25 +810,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4363</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -837,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581271</v>
+        <v>581228</v>
       </c>
       <c r="R3" t="n">
-        <v>6509584</v>
+        <v>6509602</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -872,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119930937</v>
+        <v>119930952</v>
       </c>
       <c r="B4" t="n">
-        <v>91902</v>
+        <v>96888</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,34 +925,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -956,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581288</v>
+        <v>581256</v>
       </c>
       <c r="R4" t="n">
-        <v>6509503</v>
+        <v>6509395</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -991,7 +996,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +1006,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119930948</v>
+        <v>119930953</v>
       </c>
       <c r="B5" t="n">
-        <v>94704</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,38 +1049,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581271</v>
+        <v>581280</v>
       </c>
       <c r="R5" t="n">
-        <v>6509584</v>
+        <v>6509285</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1107,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1265,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119930949</v>
+        <v>119930930</v>
       </c>
       <c r="B7" t="n">
-        <v>94704</v>
+        <v>91854</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,27 +1286,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>4363</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1309,13 +1313,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581228</v>
+        <v>581271</v>
       </c>
       <c r="R7" t="n">
-        <v>6509602</v>
+        <v>6509584</v>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1344,7 +1348,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1358,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119930913</v>
+        <v>119930907</v>
       </c>
       <c r="B8" t="n">
-        <v>90984</v>
+        <v>58176</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,30 +1401,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5420</v>
+        <v>208249</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1428,10 +1434,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581228</v>
+        <v>581287</v>
       </c>
       <c r="R8" t="n">
-        <v>6509602</v>
+        <v>6509543</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1463,7 +1469,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1473,7 +1479,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1500,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119930900</v>
+        <v>119930923</v>
       </c>
       <c r="B9" t="n">
-        <v>5189</v>
+        <v>91854</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1516,43 +1522,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>4363</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581228</v>
+        <v>581280</v>
       </c>
       <c r="R9" t="n">
-        <v>6509602</v>
+        <v>6509285</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1584,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,7 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119930939</v>
+        <v>119930946</v>
       </c>
       <c r="B10" t="n">
-        <v>91902</v>
+        <v>94704</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1633,34 +1641,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1668,10 +1673,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581163</v>
+        <v>581271</v>
       </c>
       <c r="R10" t="n">
-        <v>6509559</v>
+        <v>6509584</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1703,7 +1708,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1713,7 +1718,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1740,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119930944</v>
+        <v>119930938</v>
       </c>
       <c r="B11" t="n">
-        <v>94704</v>
+        <v>91902</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1752,49 +1757,48 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581299</v>
+        <v>581280</v>
       </c>
       <c r="R11" t="n">
-        <v>6509583</v>
+        <v>6509285</v>
       </c>
       <c r="S11" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1823,7 +1827,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1833,12 +1837,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2 kuddar</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1865,10 +1864,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119930921</v>
+        <v>119930937</v>
       </c>
       <c r="B12" t="n">
-        <v>91203</v>
+        <v>91902</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1877,25 +1876,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6031</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1912,13 +1911,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581280</v>
+        <v>581288</v>
       </c>
       <c r="R12" t="n">
-        <v>6509285</v>
+        <v>6509503</v>
       </c>
       <c r="S12" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1947,7 +1946,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1957,7 +1956,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1984,10 +1983,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119930950</v>
+        <v>119930921</v>
       </c>
       <c r="B13" t="n">
-        <v>91858</v>
+        <v>91203</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2000,31 +1999,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
@@ -2034,7 +2036,7 @@
         <v>6509285</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2063,7 +2065,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2073,7 +2075,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2100,7 +2102,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119930945</v>
+        <v>119930955</v>
       </c>
       <c r="B14" t="n">
         <v>94704</v>
@@ -2135,26 +2137,22 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581292</v>
+        <v>581280</v>
       </c>
       <c r="R14" t="n">
-        <v>6509594</v>
+        <v>6509285</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2183,7 +2181,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2193,7 +2191,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2220,10 +2218,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119930907</v>
+        <v>119930900</v>
       </c>
       <c r="B15" t="n">
-        <v>58176</v>
+        <v>5189</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2236,21 +2234,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208249</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2269,10 +2267,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581287</v>
+        <v>581228</v>
       </c>
       <c r="R15" t="n">
-        <v>6509543</v>
+        <v>6509602</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2304,7 +2302,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2314,7 +2312,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2341,10 +2339,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119930952</v>
+        <v>119930949</v>
       </c>
       <c r="B16" t="n">
-        <v>96888</v>
+        <v>94704</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2357,29 +2355,25 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221946</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2389,13 +2383,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581256</v>
+        <v>581228</v>
       </c>
       <c r="R16" t="n">
-        <v>6509395</v>
+        <v>6509602</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2424,7 +2418,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2434,7 +2428,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2461,7 +2455,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119930955</v>
+        <v>119930945</v>
       </c>
       <c r="B17" t="n">
         <v>94704</v>
@@ -2496,22 +2490,26 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581280</v>
+        <v>581292</v>
       </c>
       <c r="R17" t="n">
-        <v>6509285</v>
+        <v>6509594</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2540,7 +2538,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2550,7 +2548,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2577,10 +2575,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119930905</v>
+        <v>119930944</v>
       </c>
       <c r="B18" t="n">
-        <v>57473</v>
+        <v>94704</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2589,53 +2587,49 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581280</v>
+        <v>581299</v>
       </c>
       <c r="R18" t="n">
-        <v>6509285</v>
+        <v>6509583</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2664,7 +2658,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2674,7 +2668,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2 kuddar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2701,10 +2700,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119930936</v>
+        <v>119930933</v>
       </c>
       <c r="B19" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2713,25 +2712,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2744,13 +2743,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581269</v>
+        <v>581271</v>
       </c>
       <c r="R19" t="n">
-        <v>6509448</v>
+        <v>6509584</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2779,7 +2778,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2789,7 +2788,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2816,10 +2815,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119930923</v>
+        <v>119930905</v>
       </c>
       <c r="B20" t="n">
-        <v>91854</v>
+        <v>57473</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2828,38 +2827,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4363</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2939,10 +2939,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119930933</v>
+        <v>119930936</v>
       </c>
       <c r="B21" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2951,25 +2951,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2982,13 +2982,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581271</v>
+        <v>581269</v>
       </c>
       <c r="R21" t="n">
-        <v>6509584</v>
+        <v>6509448</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 37422-2024 artfynd.xlsx
+++ b/artfynd/A 37422-2024 artfynd.xlsx
@@ -1506,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119930923</v>
+        <v>119930946</v>
       </c>
       <c r="B9" t="n">
-        <v>91854</v>
+        <v>94704</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1522,45 +1522,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4363</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581280</v>
+        <v>581271</v>
       </c>
       <c r="R9" t="n">
-        <v>6509285</v>
+        <v>6509584</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1592,7 +1585,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1595,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,10 +1622,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119930946</v>
+        <v>119930923</v>
       </c>
       <c r="B10" t="n">
-        <v>94704</v>
+        <v>91854</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1645,38 +1638,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>4363</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581271</v>
+        <v>581280</v>
       </c>
       <c r="R10" t="n">
-        <v>6509584</v>
+        <v>6509285</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2102,10 +2102,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119930955</v>
+        <v>119930900</v>
       </c>
       <c r="B14" t="n">
-        <v>94704</v>
+        <v>5189</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2118,38 +2118,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2180</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581280</v>
+        <v>581228</v>
       </c>
       <c r="R14" t="n">
-        <v>6509285</v>
+        <v>6509602</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2181,7 +2186,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2191,7 +2196,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2218,10 +2223,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119930900</v>
+        <v>119930955</v>
       </c>
       <c r="B15" t="n">
-        <v>5189</v>
+        <v>94704</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2234,43 +2239,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581228</v>
+        <v>581280</v>
       </c>
       <c r="R15" t="n">
-        <v>6509602</v>
+        <v>6509285</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 37422-2024 artfynd.xlsx
+++ b/artfynd/A 37422-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119930939</v>
+        <v>119930945</v>
       </c>
       <c r="B2" t="n">
-        <v>91902</v>
+        <v>94704</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,6 +715,7 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581163</v>
+        <v>581292</v>
       </c>
       <c r="R2" t="n">
-        <v>6509559</v>
+        <v>6509594</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119930913</v>
+        <v>119930930</v>
       </c>
       <c r="B3" t="n">
-        <v>90984</v>
+        <v>91854</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,29 +811,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>4363</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -841,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581228</v>
+        <v>581271</v>
       </c>
       <c r="R3" t="n">
-        <v>6509602</v>
+        <v>6509584</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -876,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119930952</v>
+        <v>119930950</v>
       </c>
       <c r="B4" t="n">
-        <v>96888</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,42 +926,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581256</v>
+        <v>581280</v>
       </c>
       <c r="R4" t="n">
-        <v>6509395</v>
+        <v>6509285</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -996,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1006,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119930953</v>
+        <v>119930900</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
+        <v>5189</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,38 +1042,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581280</v>
+        <v>581228</v>
       </c>
       <c r="R5" t="n">
-        <v>6509285</v>
+        <v>6509602</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1112,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119930894</v>
+        <v>119930937</v>
       </c>
       <c r="B6" t="n">
-        <v>4772</v>
+        <v>91902</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,25 +1159,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1189,19 +1187,17 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581280</v>
+        <v>581288</v>
       </c>
       <c r="R6" t="n">
-        <v>6509285</v>
+        <v>6509503</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1233,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119930930</v>
+        <v>119930952</v>
       </c>
       <c r="B7" t="n">
-        <v>91854</v>
+        <v>96888</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,26 +1282,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4363</v>
+        <v>221946</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1313,10 +1314,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581271</v>
+        <v>581256</v>
       </c>
       <c r="R7" t="n">
-        <v>6509584</v>
+        <v>6509395</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1348,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1358,7 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119930907</v>
+        <v>119930939</v>
       </c>
       <c r="B8" t="n">
-        <v>58176</v>
+        <v>91902</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,25 +1398,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208249</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1425,8 +1426,6 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1434,10 +1433,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581287</v>
+        <v>581163</v>
       </c>
       <c r="R8" t="n">
-        <v>6509543</v>
+        <v>6509559</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1469,7 +1468,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,7 +1478,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119930946</v>
+        <v>119930894</v>
       </c>
       <c r="B9" t="n">
-        <v>94704</v>
+        <v>4772</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1522,38 +1521,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>102306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581271</v>
+        <v>581280</v>
       </c>
       <c r="R9" t="n">
-        <v>6509584</v>
+        <v>6509285</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1585,7 +1589,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1595,7 +1599,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1622,10 +1626,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119930923</v>
+        <v>119930905</v>
       </c>
       <c r="B10" t="n">
-        <v>91854</v>
+        <v>57473</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1634,38 +1638,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4363</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1708,7 +1713,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1718,7 +1723,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,10 +1750,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119930938</v>
+        <v>119930907</v>
       </c>
       <c r="B11" t="n">
-        <v>91902</v>
+        <v>58176</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,45 +1762,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>208249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581280</v>
+        <v>581287</v>
       </c>
       <c r="R11" t="n">
-        <v>6509285</v>
+        <v>6509543</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1827,7 +1834,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1837,7 +1844,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1864,10 +1871,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119930937</v>
+        <v>119930936</v>
       </c>
       <c r="B12" t="n">
-        <v>91902</v>
+        <v>91881</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1880,28 +1887,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1911,13 +1914,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581288</v>
+        <v>581269</v>
       </c>
       <c r="R12" t="n">
-        <v>6509503</v>
+        <v>6509448</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1946,7 +1949,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1956,7 +1959,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1983,10 +1986,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119930921</v>
+        <v>119930948</v>
       </c>
       <c r="B13" t="n">
-        <v>91203</v>
+        <v>94704</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1999,30 +2002,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6031</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581280</v>
+        <v>581271</v>
       </c>
       <c r="R13" t="n">
-        <v>6509285</v>
+        <v>6509584</v>
       </c>
       <c r="S13" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2102,10 +2102,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119930900</v>
+        <v>119930921</v>
       </c>
       <c r="B14" t="n">
-        <v>5189</v>
+        <v>91203</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2118,21 +2118,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>6031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2142,8 +2142,6 @@
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2151,13 +2149,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581228</v>
+        <v>581280</v>
       </c>
       <c r="R14" t="n">
-        <v>6509602</v>
+        <v>6509285</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2186,7 +2184,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2196,7 +2194,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2223,7 +2221,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119930955</v>
+        <v>119930949</v>
       </c>
       <c r="B15" t="n">
         <v>94704</v>
@@ -2256,24 +2254,24 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581280</v>
+        <v>581228</v>
       </c>
       <c r="R15" t="n">
-        <v>6509285</v>
+        <v>6509602</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2302,7 +2300,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2312,7 +2310,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2339,10 +2337,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119930949</v>
+        <v>119930923</v>
       </c>
       <c r="B16" t="n">
-        <v>94704</v>
+        <v>91854</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2355,41 +2353,48 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>4363</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581228</v>
+        <v>581280</v>
       </c>
       <c r="R16" t="n">
-        <v>6509602</v>
+        <v>6509285</v>
       </c>
       <c r="S16" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2418,7 +2423,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2428,7 +2433,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2455,7 +2460,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119930945</v>
+        <v>119930955</v>
       </c>
       <c r="B17" t="n">
         <v>94704</v>
@@ -2490,26 +2495,22 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581292</v>
+        <v>581280</v>
       </c>
       <c r="R17" t="n">
-        <v>6509594</v>
+        <v>6509285</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2538,7 +2539,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2548,7 +2549,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2700,10 +2701,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119930933</v>
+        <v>119930938</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2712,41 +2713,45 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581271</v>
+        <v>581280</v>
       </c>
       <c r="R19" t="n">
-        <v>6509584</v>
+        <v>6509285</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2778,7 +2783,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2788,7 +2793,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2815,10 +2820,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119930905</v>
+        <v>119930933</v>
       </c>
       <c r="B20" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2827,50 +2832,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581280</v>
+        <v>581271</v>
       </c>
       <c r="R20" t="n">
-        <v>6509285</v>
+        <v>6509584</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2902,7 +2898,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2912,7 +2908,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2939,10 +2935,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119930936</v>
+        <v>119930913</v>
       </c>
       <c r="B21" t="n">
-        <v>91881</v>
+        <v>90984</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2951,29 +2947,33 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -2982,13 +2982,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581269</v>
+        <v>581228</v>
       </c>
       <c r="R21" t="n">
-        <v>6509448</v>
+        <v>6509602</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 37422-2024 artfynd.xlsx
+++ b/artfynd/A 37422-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119930945</v>
+        <v>119930939</v>
       </c>
       <c r="B2" t="n">
-        <v>94704</v>
+        <v>91902</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,6 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581292</v>
+        <v>581163</v>
       </c>
       <c r="R2" t="n">
-        <v>6509594</v>
+        <v>6509559</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -910,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119930950</v>
+        <v>119930936</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,45 +921,44 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581280</v>
+        <v>581269</v>
       </c>
       <c r="R4" t="n">
-        <v>6509285</v>
+        <v>6509448</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1147,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119930937</v>
+        <v>119930949</v>
       </c>
       <c r="B6" t="n">
-        <v>91902</v>
+        <v>94704</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,34 +1157,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1194,13 +1189,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581288</v>
+        <v>581228</v>
       </c>
       <c r="R6" t="n">
-        <v>6509503</v>
+        <v>6509602</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119930952</v>
+        <v>119930921</v>
       </c>
       <c r="B7" t="n">
-        <v>96888</v>
+        <v>91203</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,31 +1277,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221946</v>
+        <v>6031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1314,13 +1308,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581256</v>
+        <v>581280</v>
       </c>
       <c r="R7" t="n">
-        <v>6509395</v>
+        <v>6509285</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1349,7 +1343,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1353,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,10 +1380,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119930939</v>
+        <v>119930894</v>
       </c>
       <c r="B8" t="n">
-        <v>91902</v>
+        <v>4772</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,25 +1392,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>102306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1426,17 +1420,19 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581163</v>
+        <v>581280</v>
       </c>
       <c r="R8" t="n">
-        <v>6509559</v>
+        <v>6509285</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1468,7 +1464,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1478,7 +1474,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119930894</v>
+        <v>119930952</v>
       </c>
       <c r="B9" t="n">
-        <v>4772</v>
+        <v>96888</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,43 +1517,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102306</v>
+        <v>221946</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581280</v>
+        <v>581256</v>
       </c>
       <c r="R9" t="n">
-        <v>6509285</v>
+        <v>6509395</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1589,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1599,7 +1594,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1626,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119930905</v>
+        <v>119930933</v>
       </c>
       <c r="B10" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1638,50 +1633,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581280</v>
+        <v>581271</v>
       </c>
       <c r="R10" t="n">
-        <v>6509285</v>
+        <v>6509584</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1713,7 +1699,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1723,7 +1709,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1750,10 +1736,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119930907</v>
+        <v>119930953</v>
       </c>
       <c r="B11" t="n">
-        <v>58176</v>
+        <v>91858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1766,43 +1752,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208249</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>51</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581287</v>
+        <v>581280</v>
       </c>
       <c r="R11" t="n">
-        <v>6509543</v>
+        <v>6509285</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1834,7 +1815,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1844,7 +1825,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1871,10 +1852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119930936</v>
+        <v>119930923</v>
       </c>
       <c r="B12" t="n">
-        <v>91881</v>
+        <v>91854</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1883,44 +1864,52 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>4363</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581269</v>
+        <v>581280</v>
       </c>
       <c r="R12" t="n">
-        <v>6509448</v>
+        <v>6509285</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1949,7 +1938,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1959,7 +1948,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1986,10 +1975,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119930948</v>
+        <v>119930913</v>
       </c>
       <c r="B13" t="n">
-        <v>94704</v>
+        <v>90984</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2002,27 +1991,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2030,10 +2022,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581271</v>
+        <v>581228</v>
       </c>
       <c r="R13" t="n">
-        <v>6509584</v>
+        <v>6509602</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2065,7 +2057,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2075,7 +2067,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2102,10 +2094,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119930921</v>
+        <v>119930946</v>
       </c>
       <c r="B14" t="n">
-        <v>91203</v>
+        <v>94704</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2118,30 +2110,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6031</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2149,13 +2138,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581280</v>
+        <v>581271</v>
       </c>
       <c r="R14" t="n">
-        <v>6509285</v>
+        <v>6509584</v>
       </c>
       <c r="S14" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2184,7 +2173,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2194,7 +2183,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2221,7 +2210,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119930949</v>
+        <v>119930944</v>
       </c>
       <c r="B15" t="n">
         <v>94704</v>
@@ -2254,7 +2243,11 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -2265,10 +2258,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581228</v>
+        <v>581299</v>
       </c>
       <c r="R15" t="n">
-        <v>6509602</v>
+        <v>6509583</v>
       </c>
       <c r="S15" t="n">
         <v>30</v>
@@ -2300,7 +2293,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2310,7 +2303,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2 kuddar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2337,10 +2335,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119930923</v>
+        <v>119930905</v>
       </c>
       <c r="B16" t="n">
-        <v>91854</v>
+        <v>57473</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2349,38 +2347,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4363</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2423,7 +2422,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2433,7 +2432,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2460,7 +2459,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119930955</v>
+        <v>119930945</v>
       </c>
       <c r="B17" t="n">
         <v>94704</v>
@@ -2495,22 +2494,26 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581280</v>
+        <v>581292</v>
       </c>
       <c r="R17" t="n">
-        <v>6509285</v>
+        <v>6509594</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2539,7 +2542,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2549,7 +2552,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2576,10 +2579,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119930944</v>
+        <v>119930907</v>
       </c>
       <c r="B18" t="n">
-        <v>94704</v>
+        <v>58176</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2592,31 +2595,32 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>208249</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2624,13 +2628,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581299</v>
+        <v>581287</v>
       </c>
       <c r="R18" t="n">
-        <v>6509583</v>
+        <v>6509543</v>
       </c>
       <c r="S18" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2659,7 +2663,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2669,12 +2673,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>2 kuddar</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2701,10 +2700,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119930938</v>
+        <v>119930955</v>
       </c>
       <c r="B19" t="n">
-        <v>91902</v>
+        <v>94704</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2713,35 +2712,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5449</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rökenskärr, Srm</t>
@@ -2783,7 +2779,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2793,7 +2789,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2820,10 +2816,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119930933</v>
+        <v>119930938</v>
       </c>
       <c r="B20" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2832,41 +2828,45 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581271</v>
+        <v>581280</v>
       </c>
       <c r="R20" t="n">
-        <v>6509584</v>
+        <v>6509285</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2935,10 +2935,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119930913</v>
+        <v>119930937</v>
       </c>
       <c r="B21" t="n">
-        <v>90984</v>
+        <v>91902</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2947,33 +2947,33 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5420</v>
+        <v>5449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581228</v>
+        <v>581288</v>
       </c>
       <c r="R21" t="n">
-        <v>6509602</v>
+        <v>6509503</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 37422-2024 artfynd.xlsx
+++ b/artfynd/A 37422-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,46 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119930939</v>
+        <v>119930944</v>
       </c>
       <c r="B2" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581163</v>
+        <v>581299</v>
       </c>
       <c r="R2" t="n">
-        <v>6509559</v>
+        <v>6509583</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2 kuddar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,15 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119930930</v>
+        <v>119930945</v>
       </c>
       <c r="B3" t="n">
-        <v>91854</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,26 +806,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4363</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581271</v>
+        <v>581292</v>
       </c>
       <c r="R3" t="n">
-        <v>6509584</v>
+        <v>6509594</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,42 +910,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119930936</v>
+        <v>119930946</v>
       </c>
       <c r="B4" t="n">
-        <v>91881</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581269</v>
+        <v>581271</v>
       </c>
       <c r="R4" t="n">
-        <v>6509448</v>
+        <v>6509584</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,15 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119930900</v>
+        <v>119930949</v>
       </c>
       <c r="B5" t="n">
-        <v>5189</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,32 +1032,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1079,7 +1066,7 @@
         <v>6509602</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1145,15 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119930949</v>
+        <v>119930955</v>
       </c>
       <c r="B6" t="n">
-        <v>94704</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,24 +1160,24 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581228</v>
+        <v>581280</v>
       </c>
       <c r="R6" t="n">
-        <v>6509602</v>
+        <v>6509285</v>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,7 +1206,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1216,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,15 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119930921</v>
+        <v>120101891</v>
       </c>
       <c r="B7" t="n">
-        <v>91203</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,21 +1254,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6031</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1301,20 +1278,21 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Kolmården, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581280</v>
+        <v>581427</v>
       </c>
       <c r="R7" t="n">
-        <v>6509285</v>
+        <v>6509036</v>
       </c>
       <c r="S7" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1338,22 +1316,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,15 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119930894</v>
+        <v>119930923</v>
       </c>
       <c r="B8" t="n">
-        <v>4772</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,32 +1369,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102306</v>
+        <v>4363</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1464,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1474,7 +1449,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,15 +1476,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119930952</v>
+        <v>119930929</v>
       </c>
       <c r="B9" t="n">
-        <v>96888</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,31 +1487,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221946</v>
+        <v>4363</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1549,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581256</v>
+        <v>581271</v>
       </c>
       <c r="R9" t="n">
-        <v>6509395</v>
+        <v>6509584</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1584,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,16 +1589,11 @@
         <v>119930933</v>
       </c>
       <c r="B10" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1736,19 +1696,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119930953</v>
+        <v>119930950</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1771,7 +1726,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1815,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1825,7 +1780,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,15 +1807,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119930923</v>
+        <v>119930913</v>
       </c>
       <c r="B12" t="n">
-        <v>91854</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1868,28 +1818,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4363</v>
+        <v>5420</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1899,14 +1845,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581280</v>
+        <v>581228</v>
       </c>
       <c r="R12" t="n">
-        <v>6509285</v>
+        <v>6509602</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1938,7 +1884,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1948,7 +1894,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1975,45 +1921,36 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119930913</v>
+        <v>119930936</v>
       </c>
       <c r="B13" t="n">
-        <v>90984</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5420</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -2022,13 +1959,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581228</v>
+        <v>581269</v>
       </c>
       <c r="R13" t="n">
-        <v>6509602</v>
+        <v>6509448</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2057,7 +1994,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2067,7 +2004,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2094,54 +2031,56 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119930946</v>
+        <v>120101888</v>
       </c>
       <c r="B14" t="n">
-        <v>94704</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Kolmården, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581271</v>
+        <v>581427</v>
       </c>
       <c r="R14" t="n">
-        <v>6509584</v>
+        <v>6509036</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2168,22 +2107,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2210,15 +2149,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119930944</v>
+        <v>119930921</v>
       </c>
       <c r="B15" t="n">
-        <v>94704</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2226,31 +2160,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>6031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2258,13 +2191,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581299</v>
+        <v>581280</v>
       </c>
       <c r="R15" t="n">
-        <v>6509583</v>
+        <v>6509285</v>
       </c>
       <c r="S15" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2293,7 +2226,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2303,12 +2236,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2 kuddar</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2335,37 +2263,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119930905</v>
+        <v>120101885</v>
       </c>
       <c r="B16" t="n">
-        <v>57473</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2383,14 +2306,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Kolmården, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581280</v>
+        <v>581427</v>
       </c>
       <c r="R16" t="n">
-        <v>6509285</v>
+        <v>6509036</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2417,22 +2340,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2459,15 +2382,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119930945</v>
+        <v>119930894</v>
       </c>
       <c r="B17" t="n">
-        <v>94704</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,21 +2393,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>102306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2500,20 +2418,21 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581292</v>
+        <v>581280</v>
       </c>
       <c r="R17" t="n">
-        <v>6509594</v>
+        <v>6509285</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2542,7 +2461,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2552,7 +2471,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2579,37 +2498,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119930907</v>
+        <v>119930905</v>
       </c>
       <c r="B18" t="n">
-        <v>58176</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>208249</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2617,21 +2531,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rökenskärr, Rökenskärr, Srm</t>
+          <t>Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581287</v>
+        <v>581280</v>
       </c>
       <c r="R18" t="n">
-        <v>6509543</v>
+        <v>6509285</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2663,7 +2580,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2673,7 +2590,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2700,15 +2617,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119930955</v>
+        <v>119930900</v>
       </c>
       <c r="B19" t="n">
-        <v>94704</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2716,38 +2628,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581280</v>
+        <v>581228</v>
       </c>
       <c r="R19" t="n">
-        <v>6509285</v>
+        <v>6509602</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2779,7 +2696,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2789,7 +2706,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2816,57 +2733,58 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119930938</v>
+        <v>120101884</v>
       </c>
       <c r="B20" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5449</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rökenskärr, Srm</t>
+          <t>Kolmården, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581280</v>
+        <v>581427</v>
       </c>
       <c r="R20" t="n">
-        <v>6509285</v>
+        <v>6509036</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2893,22 +2811,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2935,37 +2853,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119930937</v>
+        <v>119930907</v>
       </c>
       <c r="B21" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>208249</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2975,6 +2888,8 @@
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2982,10 +2897,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581288</v>
+        <v>581287</v>
       </c>
       <c r="R21" t="n">
-        <v>6509503</v>
+        <v>6509543</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3017,7 +2932,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3027,7 +2942,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3051,6 +2966,121 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>119930952</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Rökenskärr, Rökenskärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>581256</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6509395</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37422-2024 artfynd.xlsx
+++ b/artfynd/A 37422-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119930944</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119930945</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1033,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119930946</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,6 +1149,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119930949</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1240,6 +1265,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119930955</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1355,6 +1385,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120101891</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1473,6 +1508,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119930923</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1583,6 +1623,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119930929</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1693,6 +1738,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119930933</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1804,6 +1854,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119930950</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1918,6 +1973,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119930913</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2028,6 +2088,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119930936</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2146,6 +2211,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120101888</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2260,6 +2330,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119930921</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2379,6 +2454,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120101885</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2495,6 +2575,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119930894</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2614,6 +2699,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119930905</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2730,6 +2820,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119930900</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2850,6 +2945,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120101884</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2966,6 +3066,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119930907</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3081,8 +3186,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119930952</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>